--- a/questionnaire_templates/037_life_history_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/037_life_history_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Occupationearlylife</t>
+          <t>Occupation in Early Life</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Occupationcurrent</t>
+          <t>Current Occupation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Educationearlylife</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Familystatus</t>
+          <t>Family Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Employmentearlylife</t>
+          <t>Employment in Early Life</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Residencetimeline</t>
+          <t>Place of Residence</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>occupation_current</t>
+          <t>employment_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Occupationcurrent</t>
+          <t>Employment Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>education_early_life</t>
+          <t>family_income</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Educationearlylife</t>
+          <t>Family Income</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employment_status</t>
+          <t>family_type</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Employmentstatus</t>
+          <t>Family Type</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>marital_status</t>
+          <t>family_size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maritalstatus</t>
+          <t>Family Size</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>residence_status</t>
+          <t>family_income_early_life</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Residencetimeline</t>
+          <t>Family Income in Early Life</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>income_early_life</t>
+          <t>family_income_current</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Incomeearlylife</t>
+          <t>Family Income Current</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>employment_early_life</t>
+          <t>family_size_early_life</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Employmentearlylife</t>
+          <t>Family Size in Early Life</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>family_income</t>
+          <t>family_income_current_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Familysupport</t>
+          <t>Family Income Current 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>family_income</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Familysupport</t>
+          <t>Marital Status</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>family_type</t>
+          <t>employment_early_life_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Familytype</t>
+          <t>Employment Early Life 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>family_size</t>
+          <t>family_income_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Familiesize</t>
+          <t>Family Income 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>family_income</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Familysupport</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>family_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Familytype</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>family_income</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Familysupport</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>family_size</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Familiesize</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>family_income</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Familysupport</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>family_income</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Familysupport</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>employment_status</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Employmentstatus</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1216,46 +1055,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Self employed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>education_early_life_choices</t>
+          <t>occupation_current_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>education_early_life_choices</t>
+          <t>occupation_current_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>College</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1284,46 +1123,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>College</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>family_status_choices</t>
+          <t>education_early_life_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>University</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>family_status_choices</t>
+          <t>education_early_life_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>in_a_relationship</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>In a relationship</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>separated</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Separated</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>divorced</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Divorced</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1386,46 +1225,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>widowed</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Widowed</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>employment_early_life_choices</t>
+          <t>family_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>employment_early_life_choices</t>
+          <t>family_status_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>self_employed</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Self employed</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1454,114 +1293,114 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Self employed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>residence_early_life_choices</t>
+          <t>employment_early_life_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>residence_early_life_choices</t>
+          <t>employment_early_life_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>occupation_current_choices</t>
+          <t>residence_early_life_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rural</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>occupation_current_choices</t>
+          <t>residence_early_life_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Urban</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>education_early_life_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>education_early_life_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1573,675 +1412,539 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>family_income_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>unemployed</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unemployed</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>family_income_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>marital_status_choices</t>
+          <t>family_type_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>nuclear_family</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Nuclear family</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>marital_status_choices</t>
+          <t>family_type_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>single_parent_family</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Married</t>
+          <t>Single parent family</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>marital_status_choices</t>
+          <t>family_type_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>separated</t>
+          <t>other_family</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Separated</t>
+          <t>Other family</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>marital_status_choices</t>
+          <t>family_size_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>divorced</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Divorced</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>marital_status_choices</t>
+          <t>family_size_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>widowed</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Widowed</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>residence_status_choices</t>
+          <t>family_size_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>5-6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>residence_status_choices</t>
+          <t>family_size_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>7_or_more</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>7 or more</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_early_life_choices</t>
+          <t>family_income_early_life_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_early_life_choices</t>
+          <t>family_income_early_life_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>employment_early_life_choices</t>
+          <t>family_income_current_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>employment_early_life_choices</t>
+          <t>family_income_current_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>self_employed</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Self employed</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>employment_early_life_choices</t>
+          <t>family_size_early_life_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>employment_early_life_choices</t>
+          <t>family_size_early_life_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>family_income_choices</t>
+          <t>family_size_early_life_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5-6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>family_income_choices</t>
+          <t>family_size_early_life_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>7_or_more</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7 or more</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>family_type_choices</t>
+          <t>family_income_current_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nuclearfamily</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nuclearfamily</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>family_type_choices</t>
+          <t>family_income_current_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>single_parent_family</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Single parent family</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>family_type_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>other_family</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Other family</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>family_size_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>family_size_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>family_size_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>family_size_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7_or_more</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7 or more</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>family_income_choices</t>
+          <t>marital_status_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>family_income_choices</t>
+          <t>employment_early_life_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>family_type_choices</t>
+          <t>employment_early_life_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Self employed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>family_type_choices</t>
+          <t>employment_early_life_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>family_income_choices</t>
+          <t>employment_early_life_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>family_income_choices</t>
+          <t>family_income_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>family_size_choices</t>
+          <t>family_income_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>family_size_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>family_income_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>family_income_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>family_income_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>family_income_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>employment_status_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>employed</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Employed</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>employment_status_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>unemployed</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Unemployed</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>employment_status_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
